--- a/historicos/variaveis.xlsx
+++ b/historicos/variaveis.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\48197\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danma\OneDrive\Área de Trabalho\he-sbc\historicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F17BDF-748E-4A0C-8F48-C77D8F0F5E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="95">
   <si>
     <t>{ATO_DE_CRIACAO}</t>
   </si>
@@ -95,12 +96,6 @@
     <t>{ANO_HISTORICO}</t>
   </si>
   <si>
-    <t>HISTÓRICO</t>
-  </si>
-  <si>
-    <t>Concluinte, Transferência, Outra Rede</t>
-  </si>
-  <si>
     <t>DESCRIÇÃO</t>
   </si>
   <si>
@@ -149,9 +144,6 @@
     <t>{DATA}</t>
   </si>
   <si>
-    <t>Componentes curriculares, variáveis do 1 ao 11</t>
-  </si>
-  <si>
     <t>Resolução de conclusão, variáveis do 1 ao 5</t>
   </si>
   <si>
@@ -176,26 +168,164 @@
     <t>Observações do histórico.</t>
   </si>
   <si>
-    <t>Ano de conclusão/transferência do estudante no presente histórico</t>
-  </si>
-  <si>
     <t>{ANO_CORRENTE}</t>
   </si>
   <si>
-    <t>Ano (data) do histórico</t>
-  </si>
-  <si>
     <t>Data da confecção do histórico.</t>
+  </si>
+  <si>
+    <t>SEÇÃO</t>
+  </si>
+  <si>
+    <t>{RA}</t>
+  </si>
+  <si>
+    <t>{UF_RA}</t>
+  </si>
+  <si>
+    <t>R.A do(a) estudante, formatado</t>
+  </si>
+  <si>
+    <t>UF do R.A do(a) estudante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{PROSSEGUIMENTO} </t>
+  </si>
+  <si>
+    <t>Define se conclusão ou transferência (no próximo ano/no mesmo ano)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{DATA_MATR} </t>
+  </si>
+  <si>
+    <t>{DATA_TRANSF}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{CLASSE} </t>
+  </si>
+  <si>
+    <t>{TURNO}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{ANO_TRANSF}      </t>
+  </si>
+  <si>
+    <t>{TURMA}</t>
+  </si>
+  <si>
+    <t>{FALTAS}</t>
+  </si>
+  <si>
+    <t>{DIAS_LET}</t>
+  </si>
+  <si>
+    <t>{RESOL_TRANSF_1}</t>
+  </si>
+  <si>
+    <t>Data da matrícula. Usado na transferência</t>
+  </si>
+  <si>
+    <t>Data da transferência. Usado na transferência</t>
+  </si>
+  <si>
+    <t>Nº da classe no SED. Usado na transferência</t>
+  </si>
+  <si>
+    <t>Turno. Usado na transferência</t>
+  </si>
+  <si>
+    <t>{CICLO}</t>
+  </si>
+  <si>
+    <t>Ciclo (I ou II). Usado na transferência</t>
+  </si>
+  <si>
+    <t>Turma do(a) estudante. Usado na transferência</t>
+  </si>
+  <si>
+    <t>Ano de transferência (1º, 2º etc). Usado na transferência</t>
+  </si>
+  <si>
+    <t>Ano (data. Ex: 2024, 2025) do histórico.</t>
+  </si>
+  <si>
+    <t>Ano de conclusão/transferência do estudante no presente histórico (ex: 1º, 2º)</t>
+  </si>
+  <si>
+    <t>Número de faltas até a transferência. Usado na transferência.</t>
+  </si>
+  <si>
+    <t>Número de dias letivos até a transferência. Usado na transferência.</t>
+  </si>
+  <si>
+    <t>Resolução do rendimento no 1º trismestre. Usado na transferência.</t>
+  </si>
+  <si>
+    <t>Componentes curriculares (matérias), variáveis do 1 ao 13</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_2}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_3}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_4}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_5}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_6}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_7}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_9}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_8}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_10}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_11}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_12}</t>
+  </si>
+  <si>
+    <t>{COMPONENTE_13}</t>
+  </si>
+  <si>
+    <t>{RESOLUCAO_2}</t>
+  </si>
+  <si>
+    <t>{RESOLUCAO_3}</t>
+  </si>
+  <si>
+    <t>{RESOLUCAO_4}</t>
+  </si>
+  <si>
+    <t>{RESOLUCAO_5}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -221,8 +351,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,302 +635,622 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="71.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
         <v>23</v>
-      </c>
-      <c r="C1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>24</v>
+      <c r="B3" s="1">
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>24</v>
+      <c r="B4" s="1">
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
+      <c r="B5" s="1">
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>24</v>
+      <c r="B6" s="1">
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
+      <c r="B7" s="1">
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
+      <c r="B8" s="1">
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
+      <c r="B9" s="1">
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
-        <v>24</v>
+      <c r="B10" s="1">
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
-        <v>24</v>
+      <c r="B11" s="1">
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>24</v>
+      <c r="B12" s="1">
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>24</v>
+      <c r="B13" s="1">
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>24</v>
+      <c r="B14" s="1">
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>24</v>
+      <c r="B15" s="1">
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
+        <v>50</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
+        <v>51</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
+        <v>79</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
+        <v>80</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>24</v>
+        <v>81</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
+        <v>82</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" t="s">
-        <v>24</v>
+        <v>83</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
+        <v>84</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" t="s">
-        <v>24</v>
+        <v>86</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="1">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="1">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="1">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="1">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="1">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
         <v>40</v>
       </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" t="s">
-        <v>53</v>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="1">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="1">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="1">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="1">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="1">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="1">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="1">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" s="1">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="1">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="1">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="1">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="1">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" s="1">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="1">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" s="1">
+        <v>5</v>
+      </c>
+      <c r="C52" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" s="1">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="1">
+        <v>5</v>
+      </c>
+      <c r="C54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="1">
+        <v>5</v>
+      </c>
+      <c r="C55" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/historicos/variaveis.xlsx
+++ b/historicos/variaveis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danma\OneDrive\Área de Trabalho\he-sbc\historicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F17BDF-748E-4A0C-8F48-C77D8F0F5E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DDF531-82E5-4891-B27A-08E91583E5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="162">
   <si>
     <t>{ATO_DE_CRIACAO}</t>
   </si>
@@ -45,9 +45,6 @@
     <t>{EMEB}</t>
   </si>
   <si>
-    <t>VARIÁVEL</t>
-  </si>
-  <si>
     <t>{RM}</t>
   </si>
   <si>
@@ -72,12 +69,6 @@
     <t>{A_N}</t>
   </si>
   <si>
-    <t>{COMPONENTE_1}</t>
-  </si>
-  <si>
-    <t>{RESOLUCAO_1}</t>
-  </si>
-  <si>
     <t>{HORAS_1}</t>
   </si>
   <si>
@@ -96,9 +87,6 @@
     <t>{ANO_HISTORICO}</t>
   </si>
   <si>
-    <t>DESCRIÇÃO</t>
-  </si>
-  <si>
     <t>Nome da EMEB.</t>
   </si>
   <si>
@@ -144,9 +132,6 @@
     <t>{DATA}</t>
   </si>
   <si>
-    <t>Resolução de conclusão, variáveis do 1 ao 5</t>
-  </si>
-  <si>
     <t>Horas de conclusão, variáveis do 1 ao 5</t>
   </si>
   <si>
@@ -174,9 +159,6 @@
     <t>Data da confecção do histórico.</t>
   </si>
   <si>
-    <t>SEÇÃO</t>
-  </si>
-  <si>
     <t>{RA}</t>
   </si>
   <si>
@@ -219,9 +201,6 @@
     <t>{DIAS_LET}</t>
   </si>
   <si>
-    <t>{RESOL_TRANSF_1}</t>
-  </si>
-  <si>
     <t>Data da matrícula. Usado na transferência</t>
   </si>
   <si>
@@ -258,58 +237,280 @@
     <t>Número de dias letivos até a transferência. Usado na transferência.</t>
   </si>
   <si>
-    <t>Resolução do rendimento no 1º trismestre. Usado na transferência.</t>
-  </si>
-  <si>
-    <t>Componentes curriculares (matérias), variáveis do 1 ao 13</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_2}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_3}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_4}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_5}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_6}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_7}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_9}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_8}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_10}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_11}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_12}</t>
-  </si>
-  <si>
-    <t>{COMPONENTE_13}</t>
-  </si>
-  <si>
-    <t>{RESOLUCAO_2}</t>
-  </si>
-  <si>
-    <t>{RESOLUCAO_3}</t>
-  </si>
-  <si>
-    <t>{RESOLUCAO_4}</t>
-  </si>
-  <si>
-    <t>{RESOLUCAO_5}</t>
+    <t>{#disciplinas} {nome} {/disciplinas}</t>
+  </si>
+  <si>
+    <t>Lista de componentes curriculares (matérias), precisa criar 13 linhas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{#exibirNotas} {#disciplinas} {nota} {/disciplinas} {/exibirNotas} </t>
+  </si>
+  <si>
+    <t>Exibe as notas das disciplinas</t>
+  </si>
+  <si>
+    <t>{#exibirResolucao} {TEXTO_DA_RESOLUCAO} {/exibirResolucao}</t>
+  </si>
+  <si>
+    <t>Exibe a resolução da SE, no caso de EMEB</t>
+  </si>
+  <si>
+    <t>placeholder</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>list</t>
+  </si>
+  <si>
+    <t>{HORAS_2}</t>
+  </si>
+  <si>
+    <t>{HORAS_3}</t>
+  </si>
+  <si>
+    <t>{HORAS_4}</t>
+  </si>
+  <si>
+    <t>{HORAS_5}</t>
+  </si>
+  <si>
+    <t>{ANO_2}</t>
+  </si>
+  <si>
+    <t>{ANO_3}</t>
+  </si>
+  <si>
+    <t>{ANO_4}</t>
+  </si>
+  <si>
+    <t>{ANO_5}</t>
+  </si>
+  <si>
+    <t>{ESCOLA_2}</t>
+  </si>
+  <si>
+    <t>{ESCOLA_3}</t>
+  </si>
+  <si>
+    <t>{ESCOLA_4}</t>
+  </si>
+  <si>
+    <t>{ESCOLA_5}</t>
+  </si>
+  <si>
+    <t>{MUNIC_2}</t>
+  </si>
+  <si>
+    <t>{MUNIC_3}</t>
+  </si>
+  <si>
+    <t>{MUNIC_4}</t>
+  </si>
+  <si>
+    <t>{MUNIC_5}</t>
+  </si>
+  <si>
+    <t>{UF_2}</t>
+  </si>
+  <si>
+    <t>{UF_3}</t>
+  </si>
+  <si>
+    <t>{UF_4}</t>
+  </si>
+  <si>
+    <t>{UF_5}</t>
+  </si>
+  <si>
+    <t>Ano de conclusão do 2º ano, variáveis do 1 ao 5</t>
+  </si>
+  <si>
+    <t>Ano de conclusão do 3º ano, variáveis do 1 ao 5</t>
+  </si>
+  <si>
+    <t>Ano de conclusão do 4º ano, variáveis do 1 ao 5</t>
+  </si>
+  <si>
+    <t>Ano de conclusão do 5º ano, variáveis do 1 ao 5</t>
+  </si>
+  <si>
+    <t>Resolução do rendimento nos trismestres. Usado na transferência.</t>
+  </si>
+  <si>
+    <t>{#exibirResolucaoTransf} {TEXTO_DA_RESOLUCAO_TRANSF} {/exibirResolucaoTransf}</t>
+  </si>
+  <si>
+    <t>form</t>
+  </si>
+  <si>
+    <t>Nome da EMEB</t>
+  </si>
+  <si>
+    <t>Endereço</t>
+  </si>
+  <si>
+    <t>CEP</t>
+  </si>
+  <si>
+    <t>Nacionalidade</t>
+  </si>
+  <si>
+    <t>UF</t>
+  </si>
+  <si>
+    <t>Telefone 1</t>
+  </si>
+  <si>
+    <t>Telefone 2</t>
+  </si>
+  <si>
+    <t>Ato de Criação da EMEB</t>
+  </si>
+  <si>
+    <t>RM</t>
+  </si>
+  <si>
+    <t>Nome do(a) Estudante</t>
+  </si>
+  <si>
+    <t>Município de Nascimento</t>
+  </si>
+  <si>
+    <t>Data de Nascimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R.A </t>
+  </si>
+  <si>
+    <t>UF do R.A</t>
+  </si>
+  <si>
+    <t>Disciplinas Estudadas</t>
+  </si>
+  <si>
+    <t>Notas das Disciplinas</t>
+  </si>
+  <si>
+    <t>Horas totais 1º ano.</t>
+  </si>
+  <si>
+    <t>Horas totais 2º ano.</t>
+  </si>
+  <si>
+    <t>Horas totais 3º ano.</t>
+  </si>
+  <si>
+    <t>Horas totais 4º ano.</t>
+  </si>
+  <si>
+    <t>Horas totais 5º ano.</t>
+  </si>
+  <si>
+    <t>Ano de Conclusão ou Transf. 1º ano</t>
+  </si>
+  <si>
+    <t>Ano de Conclusão ou Transf. 2º ano</t>
+  </si>
+  <si>
+    <t>Ano de Conclusão ou Transf. 3º ano</t>
+  </si>
+  <si>
+    <t>Ano de Conclusão ou Transf. 4º ano</t>
+  </si>
+  <si>
+    <t>Ano de Conclusão ou Transf. 5º ano</t>
+  </si>
+  <si>
+    <t>Escola de Conclusão ou Transf. 5º ano</t>
+  </si>
+  <si>
+    <t>Escola de Conclusão ou Transf. 1º ano</t>
+  </si>
+  <si>
+    <t>Escola de Conclusão ou Transf. 2º ano</t>
+  </si>
+  <si>
+    <t>Escola de Conclusão ou Transf. 3º ano</t>
+  </si>
+  <si>
+    <t>Escola de Conclusão ou Transf. 4º ano</t>
+  </si>
+  <si>
+    <t>Município de Conclusão ou Transf. 1º ano</t>
+  </si>
+  <si>
+    <t>Município de Conclusão ou Transf. 2º ano</t>
+  </si>
+  <si>
+    <t>Município de Conclusão ou Transf. 3º ano</t>
+  </si>
+  <si>
+    <t>Município de Conclusão ou Transf. 4º ano</t>
+  </si>
+  <si>
+    <t>Município de Conclusão ou Transf. 5º ano</t>
+  </si>
+  <si>
+    <t>UF Conclusão ou Transf. 1º ano</t>
+  </si>
+  <si>
+    <t>UF Conclusão ou Transf. 2º ano</t>
+  </si>
+  <si>
+    <t>UF Conclusão ou Transf. 3º ano</t>
+  </si>
+  <si>
+    <t>UF Conclusão ou Transf. 4º ano</t>
+  </si>
+  <si>
+    <t>UF Conclusão ou Transf. 5º ano</t>
+  </si>
+  <si>
+    <t>Data da Matrícula</t>
+  </si>
+  <si>
+    <t>Data da Transferência</t>
+  </si>
+  <si>
+    <t>Classe</t>
+  </si>
+  <si>
+    <t>Turno</t>
+  </si>
+  <si>
+    <t>Ciclo</t>
+  </si>
+  <si>
+    <t>Ano (1º, 2º, etc)</t>
+  </si>
+  <si>
+    <t>Turma</t>
+  </si>
+  <si>
+    <t>Faltas</t>
+  </si>
+  <si>
+    <t>Dias Letivos</t>
+  </si>
+  <si>
+    <t>Lista de Observações</t>
+  </si>
+  <si>
+    <t>Data</t>
   </si>
 </sst>
 </file>
@@ -636,617 +837,1019 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="71.140625" customWidth="1"/>
+    <col min="1" max="1" width="75.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="75.42578125" customWidth="1"/>
+    <col min="5" max="5" width="71.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
       </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
       </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
-      <c r="C18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
-      <c r="C19" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B20" s="1">
         <v>2</v>
       </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="B21" s="1">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B22" s="1">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>86</v>
       </c>
       <c r="B25" s="1">
-        <v>2</v>
-      </c>
-      <c r="C25" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="B26" s="1">
-        <v>2</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>87</v>
       </c>
       <c r="B27" s="1">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>88</v>
       </c>
       <c r="B28" s="1">
-        <v>2</v>
-      </c>
-      <c r="C28" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>89</v>
       </c>
       <c r="B29" s="1">
-        <v>2</v>
-      </c>
-      <c r="C29" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>90</v>
       </c>
       <c r="B30" s="1">
-        <v>2</v>
-      </c>
-      <c r="C30" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="1">
-        <v>2</v>
-      </c>
-      <c r="C31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" t="s">
+        <v>137</v>
+      </c>
+      <c r="E31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>91</v>
       </c>
       <c r="B32" s="1">
-        <v>2</v>
-      </c>
-      <c r="C32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>92</v>
       </c>
       <c r="B33" s="1">
-        <v>2</v>
-      </c>
-      <c r="C33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>93</v>
       </c>
       <c r="B34" s="1">
-        <v>2</v>
-      </c>
-      <c r="C34" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>94</v>
       </c>
       <c r="B35" s="1">
-        <v>2</v>
-      </c>
-      <c r="C35" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
       <c r="B36" s="1">
-        <v>2</v>
-      </c>
-      <c r="C36" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" t="s">
+        <v>142</v>
+      </c>
+      <c r="E37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="1">
+        <v>3</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="1">
+        <v>3</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="1">
+        <v>3</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="1">
-        <v>3</v>
-      </c>
-      <c r="C37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" s="1">
-        <v>3</v>
-      </c>
-      <c r="C38" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="1">
-        <v>3</v>
-      </c>
-      <c r="C39" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" s="1">
-        <v>3</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
-      </c>
       <c r="B41" s="1">
-        <v>4</v>
-      </c>
-      <c r="C41" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="B42" s="1">
-        <v>4</v>
-      </c>
-      <c r="C42" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1">
-        <v>4</v>
-      </c>
-      <c r="C43" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" t="s">
+        <v>148</v>
+      </c>
+      <c r="E43" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1">
-        <v>4</v>
-      </c>
-      <c r="C44" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="B45" s="1">
-        <v>4</v>
-      </c>
-      <c r="C45" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" t="s">
+        <v>150</v>
+      </c>
+      <c r="E45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B46" s="1">
         <v>4</v>
       </c>
-      <c r="C46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C46" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B47" s="1">
         <v>4</v>
       </c>
-      <c r="C47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B48" s="1">
         <v>4</v>
       </c>
-      <c r="C48" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C48" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D48" t="s">
+        <v>153</v>
+      </c>
+      <c r="E48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B49" s="1">
         <v>4</v>
       </c>
-      <c r="C49" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" t="s">
+        <v>154</v>
+      </c>
+      <c r="E49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B50" s="1">
         <v>4</v>
       </c>
-      <c r="C50" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D50" t="s">
+        <v>155</v>
+      </c>
+      <c r="E50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B51" s="1">
+        <v>4</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" t="s">
+        <v>156</v>
+      </c>
+      <c r="E51" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="1">
+        <v>4</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" t="s">
+        <v>157</v>
+      </c>
+      <c r="E52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="1">
+        <v>4</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" t="s">
+        <v>158</v>
+      </c>
+      <c r="E53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="1">
+        <v>4</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" t="s">
+        <v>159</v>
+      </c>
+      <c r="E54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="1">
+        <v>4</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="1">
         <v>5</v>
       </c>
-      <c r="C51" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>22</v>
-      </c>
-      <c r="B52" s="1">
+      <c r="C56" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D56" t="s">
+        <v>160</v>
+      </c>
+      <c r="E56" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57" s="1">
         <v>5</v>
       </c>
-      <c r="C52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="1">
+      <c r="C57" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E57" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="1">
         <v>5</v>
       </c>
-      <c r="C53" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54" s="1">
+      <c r="C58" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E58" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" s="1">
         <v>5</v>
       </c>
-      <c r="C54" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="1">
+      <c r="C59" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B60" s="1">
         <v>5</v>
       </c>
-      <c r="C55" t="s">
-        <v>48</v>
+      <c r="C60" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D60" t="s">
+        <v>161</v>
+      </c>
+      <c r="E60" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/historicos/variaveis.xlsx
+++ b/historicos/variaveis.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danma\OneDrive\Área de Trabalho\he-sbc\historicos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\48197\Desktop\Históricos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DDF531-82E5-4891-B27A-08E91583E5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="177">
   <si>
     <t>{ATO_DE_CRIACAO}</t>
   </si>
@@ -511,12 +510,57 @@
   </si>
   <si>
     <t>Data</t>
+  </si>
+  <si>
+    <t>{#disciplinas_diversificadas} {nome} {#disciplinas_diversificadas}</t>
+  </si>
+  <si>
+    <t>Disciplinas Diversificadas</t>
+  </si>
+  <si>
+    <t>Lista de componentes curriculares diversificados (matérias),</t>
+  </si>
+  <si>
+    <t>{#exibirResolucaoEducarMais} {TEXTO_EDUCAR_MAIS} {/ exibirResolucaoEducarMais }</t>
+  </si>
+  <si>
+    <t>{HMAIS_1}</t>
+  </si>
+  <si>
+    <t>Horas totais 1º ano EDUCAR MAIS.</t>
+  </si>
+  <si>
+    <t>Horas das matéiras diversificadas do EDUCAR MAIS, variáveis do 1 ao 5</t>
+  </si>
+  <si>
+    <t>{HMAIS_2}</t>
+  </si>
+  <si>
+    <t>{HMAIS_3}</t>
+  </si>
+  <si>
+    <t>{HMAIS_4}</t>
+  </si>
+  <si>
+    <t>{HMAIS_5}</t>
+  </si>
+  <si>
+    <t>Horas totais 2º ano EDUCAR MAIS.</t>
+  </si>
+  <si>
+    <t>Horas totais 3º ano EDUCAR MAIS.</t>
+  </si>
+  <si>
+    <t>Horas totais 4º ano EDUCAR MAIS.</t>
+  </si>
+  <si>
+    <t>Horas totais 5º ano EDUCAR MAIS.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -836,8 +880,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75.5703125" customWidth="1"/>
@@ -1186,41 +1230,35 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="B21" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="B22" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="D22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="B23" s="1">
         <v>3</v>
@@ -1229,15 +1267,15 @@
         <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="B24" s="1">
         <v>3</v>
@@ -1246,15 +1284,15 @@
         <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="B25" s="1">
         <v>3</v>
@@ -1263,100 +1301,100 @@
         <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>171</v>
       </c>
       <c r="B26" s="1">
         <v>3</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>172</v>
       </c>
       <c r="B27" s="1">
         <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="B28" s="1">
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B29" s="1">
         <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E29" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B30" s="1">
         <v>3</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="B31" s="1">
         <v>3</v>
@@ -1365,15 +1403,15 @@
         <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B32" s="1">
         <v>3</v>
@@ -1382,100 +1420,100 @@
         <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="B33" s="1">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B34" s="1">
         <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B35" s="1">
         <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="B36" s="1">
         <v>3</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B37" s="1">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="B38" s="1">
         <v>3</v>
@@ -1484,15 +1522,15 @@
         <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B39" s="1">
         <v>3</v>
@@ -1501,15 +1539,15 @@
         <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B40" s="1">
         <v>3</v>
@@ -1518,15 +1556,15 @@
         <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="B41" s="1">
         <v>3</v>
@@ -1535,15 +1573,15 @@
         <v>80</v>
       </c>
       <c r="D41" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B42" s="1">
         <v>3</v>
@@ -1552,15 +1590,15 @@
         <v>80</v>
       </c>
       <c r="D42" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E42" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="B43" s="1">
         <v>3</v>
@@ -1569,15 +1607,15 @@
         <v>80</v>
       </c>
       <c r="D43" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B44" s="1">
         <v>3</v>
@@ -1586,15 +1624,15 @@
         <v>80</v>
       </c>
       <c r="D44" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B45" s="1">
         <v>3</v>
@@ -1603,168 +1641,168 @@
         <v>80</v>
       </c>
       <c r="D45" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="B46" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D46" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E46" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="B47" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E47" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B48" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="B49" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D49" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E49" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="B50" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D50" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E50" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="B51" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D51" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E51" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B52" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D52" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E52" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B53" s="1">
         <v>4</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E53" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B54" s="1">
         <v>4</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D54" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E54" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="B55" s="1">
         <v>4</v>
@@ -1772,83 +1810,202 @@
       <c r="C55" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="D55" t="s">
+        <v>153</v>
+      </c>
       <c r="E55" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B56" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E56" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="B57" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="D57" t="s">
+        <v>155</v>
+      </c>
       <c r="E57" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B58" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="D58" t="s">
+        <v>156</v>
       </c>
       <c r="E58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B59" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="D59" t="s">
+        <v>157</v>
+      </c>
       <c r="E59" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="1">
+        <v>4</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" t="s">
+        <v>158</v>
+      </c>
+      <c r="E60" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="1">
+        <v>4</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E61" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>108</v>
+      </c>
+      <c r="B62" s="1">
+        <v>4</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E62" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="1">
+        <v>5</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63" t="s">
+        <v>160</v>
+      </c>
+      <c r="E63" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" s="1">
+        <v>5</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E64" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="1">
+        <v>5</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E65" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" s="1">
+        <v>5</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E66" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>34</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B67" s="1">
         <v>5</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="C67" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" t="s">
         <v>161</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E67" t="s">
         <v>43</v>
       </c>
     </row>
